--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2023_T1_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2023_T1_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
+    <t>50</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -63,28 +63,28 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.500</t>
-  </si>
-  <si>
-    <t>(0.067)</t>
-  </si>
-  <si>
-    <t>0.357</t>
-  </si>
-  <si>
-    <t>(0.065)</t>
-  </si>
-  <si>
-    <t>1.071</t>
-  </si>
-  <si>
-    <t>(0.194)</t>
-  </si>
-  <si>
-    <t>0.554</t>
-  </si>
-  <si>
-    <t>(0.127)</t>
+    <t>0.560</t>
+  </si>
+  <si>
+    <t>(0.071)</t>
+  </si>
+  <si>
+    <t>0.400</t>
+  </si>
+  <si>
+    <t>(0.070)</t>
+  </si>
+  <si>
+    <t>1.200</t>
+  </si>
+  <si>
+    <t>(0.210)</t>
+  </si>
+  <si>
+    <t>0.620</t>
+  </si>
+  <si>
+    <t>(0.140)</t>
   </si>
   <si>
     <t>60</t>
@@ -123,7 +123,7 @@
     <t>.n</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -135,16 +135,16 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.367***</t>
-  </si>
-  <si>
-    <t>0.326***</t>
-  </si>
-  <si>
-    <t>3.445***</t>
-  </si>
-  <si>
-    <t>1.296***</t>
+    <t>0.307***</t>
+  </si>
+  <si>
+    <t>0.283***</t>
+  </si>
+  <si>
+    <t>3.317***</t>
+  </si>
+  <si>
+    <t>1.230***</t>
   </si>
 </sst>
 </file>
